--- a/material/formr_anonymity.xlsx
+++ b/material/formr_anonymity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hochschulefresenius1-my.sharepoint.com/personal/caroline_zygar-hoffmann_charlotte-fresenius-uni_de/Documents/Lehre/WAF/WAF_Folien/material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{63D631A9-4FBF-4FC5-8CA7-40C8BF057F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B7C29A0-708D-4354-86EE-35EE6716D938}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{63D631A9-4FBF-4FC5-8CA7-40C8BF057F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{194730B4-E342-446F-8CC0-25C061381B86}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="75">
   <si>
     <t>Notes</t>
   </si>
@@ -173,15 +173,6 @@
 Mit Ausfüllen dieser Umfrage willigen Sie ein, dass die Antworten im Rahmen der Vorlesung geteilt werden. Die Antworten werden nach der nächsten Einheit gelöscht.</t>
   </si>
   <si>
-    <t>mc_button  liste_konsum</t>
-  </si>
-  <si>
-    <t>konsum</t>
-  </si>
-  <si>
-    <t>label_align_left</t>
-  </si>
-  <si>
     <t>liste_konsum</t>
   </si>
   <si>
@@ -203,9 +194,6 @@
     <t>ab 4h</t>
   </si>
   <si>
-    <t>Wie hoch schätzen sie Ihren täglichen TikTok Konsum?</t>
-  </si>
-  <si>
     <t>select_one  demo_relStat</t>
   </si>
   <si>
@@ -215,15 +203,6 @@
     <t>Sind Sie verheiratet, oder leben Sie in einer Partnerschaft mit festem Freund bzw. fester Freundin, oder sind Sie zurzeit Single, also ohne feste Partnerschaft?</t>
   </si>
   <si>
-    <t>demo_relStat == "married" || demo_relStat == "relationship"</t>
-  </si>
-  <si>
-    <t>demo_relLive</t>
-  </si>
-  <si>
-    <t>Wohnen Sie mit Ihrem Partner/ Ihrer Partnerin zusammen?</t>
-  </si>
-  <si>
     <t>married</t>
   </si>
   <si>
@@ -245,32 +224,44 @@
     <t>kA</t>
   </si>
   <si>
-    <t>mc_haustierbesitz</t>
-  </si>
-  <si>
-    <t>Haben oder hatten Sie jemals ein Haustier?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">text  </t>
-  </si>
-  <si>
-    <t>haustier</t>
-  </si>
-  <si>
-    <t>Was für ein Haustier haben/hatten Sie? (Hund, Katze….etc)</t>
-  </si>
-  <si>
-    <t>mc_haustierbesitz == 1</t>
-  </si>
-  <si>
     <t>textarea</t>
+  </si>
+  <si>
+    <t>Ich strebe derzeit den Beruf des Psychotherapeuten an</t>
+  </si>
+  <si>
+    <t>therapeut</t>
+  </si>
+  <si>
+    <t>Ich besitze einen Instagram-Account.</t>
+  </si>
+  <si>
+    <t>instagram</t>
+  </si>
+  <si>
+    <t>siblings</t>
+  </si>
+  <si>
+    <t>Haben Sie mindestens ein Geschwister?</t>
+  </si>
+  <si>
+    <t>Wohnen Sie mit Ihrem Partner in einem gemeinsamen Haushalt?</t>
+  </si>
+  <si>
+    <t>gem_haushalt</t>
+  </si>
+  <si>
+    <t>partnerschaft</t>
+  </si>
+  <si>
+    <t>partnerschaft == "married" || partnerschaft == "relationship"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,6 +306,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -475,7 +472,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -494,6 +491,14 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -623,10 +628,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -982,13 +983,13 @@
     </row>
     <row r="5" spans="1:11" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -996,13 +997,13 @@
         <v>22</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
         <v>25</v>
@@ -1011,49 +1012,60 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="C7" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7"/>
+      <c r="I7" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" s="10" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>49</v>
+    <row r="8" spans="1:11" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="I9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1109,7 +1121,7 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
         <v>28</v>
@@ -1260,13 +1272,13 @@
     </row>
     <row r="15" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B15" s="5">
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1274,7 +1286,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1282,7 +1294,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1290,7 +1302,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1298,7 +1310,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1306,42 +1318,42 @@
         <v>6</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>39</v>

--- a/material/formr_anonymity.xlsx
+++ b/material/formr_anonymity.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hochschulefresenius1-my.sharepoint.com/personal/caroline_zygar-hoffmann_charlotte-fresenius-uni_de/Documents/Lehre/WAF/WAF_Folien/material/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{63D631A9-4FBF-4FC5-8CA7-40C8BF057F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{194730B4-E342-446F-8CC0-25C061381B86}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="13_ncr:1_{63D631A9-4FBF-4FC5-8CA7-40C8BF057F32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B89CD3D-8129-4D3B-B29C-EF4314C642A2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="81">
   <si>
     <t>Notes</t>
   </si>
@@ -139,12 +139,6 @@
     <t>Single</t>
   </si>
   <si>
-    <t>Wohnen Sie in München?</t>
-  </si>
-  <si>
-    <t>wohnort</t>
-  </si>
-  <si>
     <t>Anderer</t>
   </si>
   <si>
@@ -154,13 +148,7 @@
     <t>Nennen Sie eine peinliche Sache über sich, die Sie im Rahmen der Vorlesung preisgeben würden (kann, muss aber nicht wahrheitsgemäß sein).</t>
   </si>
   <si>
-    <t>Haben Sie schonmal etwas anderes als Psychologie studiert?</t>
-  </si>
-  <si>
     <t>anderes/keine Angabe</t>
-  </si>
-  <si>
-    <t>studium</t>
   </si>
   <si>
     <t>alter</t>
@@ -227,18 +215,6 @@
     <t>textarea</t>
   </si>
   <si>
-    <t>Ich strebe derzeit den Beruf des Psychotherapeuten an</t>
-  </si>
-  <si>
-    <t>therapeut</t>
-  </si>
-  <si>
-    <t>Ich besitze einen Instagram-Account.</t>
-  </si>
-  <si>
-    <t>instagram</t>
-  </si>
-  <si>
     <t>siblings</t>
   </si>
   <si>
@@ -255,13 +231,55 @@
   </si>
   <si>
     <t>partnerschaft == "married" || partnerschaft == "relationship"</t>
+  </si>
+  <si>
+    <t>mc_width110_length80</t>
+  </si>
+  <si>
+    <t>mc</t>
+  </si>
+  <si>
+    <t>Studienerfahrung</t>
+  </si>
+  <si>
+    <t>Ich habe vor diesem Studium schon etwas anderes studiert.</t>
+  </si>
+  <si>
+    <t>Nein</t>
+  </si>
+  <si>
+    <t>Ja, begonnen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja, abgeschlossen </t>
+  </si>
+  <si>
+    <t>mc_width150</t>
+  </si>
+  <si>
+    <t>mc1_Wohnort</t>
+  </si>
+  <si>
+    <t>Wo wohnen Sie ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">auf dem Land </t>
+  </si>
+  <si>
+    <t xml:space="preserve">in der Stadt </t>
+  </si>
+  <si>
+    <t>mc2_urspWohnort</t>
+  </si>
+  <si>
+    <t>Wo sind Sie aufgewachsen?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,6 +331,20 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -472,7 +504,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -497,8 +529,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -893,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
@@ -904,10 +944,11 @@
     <col min="6" max="6" width="18.140625" customWidth="1"/>
     <col min="7" max="7" width="18.28515625" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
-    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -942,7 +983,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" s="1" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>12</v>
       </c>
@@ -950,7 +991,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
@@ -959,51 +1000,51 @@
       <c r="I2"/>
       <c r="J2"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I6" t="s">
         <v>25</v>
@@ -1012,72 +1053,114 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>22</v>
+    <row r="7" spans="1:20" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
+      <c r="B7" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7"/>
-      <c r="I7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="L7" s="11"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="12"/>
+    </row>
+    <row r="8" spans="1:20" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="8" t="s">
         <v>68</v>
       </c>
+      <c r="C8" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="D8" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>22</v>
+        <v>76</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="12"/>
+      <c r="S8" s="12"/>
+      <c r="T8" s="12"/>
+    </row>
+    <row r="9" spans="1:20" ht="65.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="I9" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H9" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
+      <c r="T9" s="12"/>
+    </row>
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
+      <c r="C10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
       <c r="I10" t="s">
         <v>25</v>
       </c>
@@ -1085,15 +1168,15 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="I11" t="s">
         <v>25</v>
@@ -1102,42 +1185,25 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="I12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1198,7 +1264,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1259,7 +1325,7 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1267,18 +1333,18 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5">
         <v>1</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1286,7 +1352,7 @@
         <v>2</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1294,7 +1360,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1302,7 +1368,7 @@
         <v>4</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1310,7 +1376,7 @@
         <v>5</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -1318,45 +1384,45 @@
         <v>6</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
